--- a/lynkk-reddit-leads/results/2026-10-11/engagement_replies_2026-10-11.xlsx
+++ b/lynkk-reddit-leads/results/2026-10-11/engagement_replies_2026-10-11.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="engagement replies" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="engagement replies" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +501,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -514,27 +514,27 @@
           <t>https://www.reddit.com/r/AIDiscussion/comments/1wymbzg/is_an_ai_meeting_assistant_saving_you_work_after/</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>r/AIDiscussion</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>u/Doug19</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Is an AI meeting assistant saving you work after the call?</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Already a lead (#19); engagement version here.</t>
         </is>
@@ -544,13 +544,13 @@
           <t>Honest answer: the summary itself rarely saves time, the structure does. When decisions, action items with owners and open questions are separate lists, 'we could try this' lands in open questions instead of being read as a decision, and checking takes a minute. The other thing that helps is saying owners and dates out loud before the call ends. What's your experience with Bluedot so far, do people actually open the summaries?</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -563,17 +563,17 @@
           <t>https://www.reddit.com/r/ProductivityApps/comments/1x1hlb5/anyone_automated_turning_meeting_notes_into/</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>r/ProductivityApps</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>u/GlitteringSuit5341</t>
         </is>
@@ -593,13 +593,13 @@
           <t>One trick that cuts this down: flag the moment during the call instead of after. A quick note like 'post idea' with the timestamp means you're not rereading the whole summary later. Then the draft step is just 'turn this quote into a LinkedIn post in my voice', which any AI does fine. Keep the founder's exact words next to the draft so you don't accidentally change what they meant before you publish. n8n can handle the hand-off once the flagged notes land somewhere consistent.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -612,22 +612,22 @@
           <t>https://www.reddit.com/r/Notion/comments/1wk288j/how_do_you_keep_a_shared_ai_meeting_notes/</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>r/Notion</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>u/Antique-Anybody-1343</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>How do you keep a shared AI Meeting Notes database clean?</t>
         </is>
@@ -642,13 +642,13 @@
           <t>This drift is really common. What usually helps is cutting properties down to the three that drive views (internal or external, team, type) and setting them from the meeting title with a naming convention like 'EXT | Acme | Discovery'. A Notion automation or a small script can then parse the title into properties, which is more reliable than mapping invitees. Attendees are worth keeping as a plain text field for search rather than a relation you have to maintain. Anyone else found a cleaner way?</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>86</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -661,17 +661,17 @@
           <t>https://www.reddit.com/r/productivity/comments/1witmm6/marketing_people_wearing_10_hats_what_have_you/</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>r/productivity</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>u/Vivi-vivi-S</t>
         </is>
@@ -691,13 +691,13 @@
           <t>A common one that sticks is the meeting step: notes come out of the call already split into decisions, action items with owners and open questions, and only the action items get pushed into the task tool after a quick human check. The check matters; fully automatic task creation tends to turn 'we could' into fake tasks. Auto-generated reports are a common one people abandon, because they end up rewriting them anyway. Boring rule: automate the handoff, not the judgement.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="n">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -710,17 +710,17 @@
           <t>https://www.reddit.com/r/HOA/comments/1wkn4pc/are_you_using_ai_to_take_your_meeting/</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>r/HOA</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>u/soshinyapp</t>
         </is>
@@ -730,7 +730,7 @@
           <t>Are you using AI to take your meeting notes-minutes [ALL] [N/A]</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>HOA board minutes poll. Engagement only.</t>
         </is>
@@ -740,13 +740,13 @@
           <t>AI can be useful for the first draft of minutes, but minutes are a legal record, so the secretary still has to own them. What works: record with the board's consent, let the tool draft motions, votes and action items, then the secretary checks each motion and vote against the recording before the draft goes out for approval. Anything the tool summarises should be checkable against the moment it was said. Where it goes wrong is when the AI summary is approved as-is.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
         <v>83</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -759,22 +759,22 @@
           <t>https://www.reddit.com/r/GenAiApps/comments/1wkxayl/id_like_meeting_apps_to_flag_tasks_with_no/</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>r/GenAiApps</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>u/lifeguard_8</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>I'd like meeting apps to flag tasks with no confirmed owner</t>
         </is>
@@ -789,13 +789,13 @@
           <t>Agree, 'agreed but unowned' deserves its own section. A habit that works well in standups is ending with a 30-second owner check: read the action items out loud and anyone unassigned gets an owner or gets dropped. Tools help most when every action item links back to the moment it came from, so you can tell 'we should ask Sam' from 'Sam said yes'. Does Vomo keep the source moment next to each item?</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="n">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -808,27 +808,27 @@
           <t>https://www.reddit.com/r/projectmanagers/comments/1wuc4j7/aigenerated_project_updates_useful_or_just_more/</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>r/projectmanagers</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>u/Kripa_HR</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>AI-generated project updates: useful or just more noise?</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>PM discussion about AI status reports.</t>
         </is>
@@ -838,13 +838,13 @@
           <t>I'd trust the draft if every line traces back to a source: the ticket, the doc or the moment in the meeting where it was said. Without that, it's another report nobody believes. What a PM still has to own is the judgement: what's actually at risk, what changed since last week, and what needs a decision from someone. AI is good at collecting the facts, much less good at deciding which two of them matter.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -857,17 +857,17 @@
           <t>https://www.reddit.com/r/ProjectCoordinators/comments/1x0tcrp/70_of_project_orgs_now_use_ai_up_from_36_two/</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>r/ProjectCoordinators</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>u/Exciting_Tip3020</t>
         </is>
@@ -889,15 +889,15 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>I work on Lynkk, so I'm biased, but that's the setup it's built for: no-bot recording on Mac or Chrome, and a brief with decisions and action items that link back to the recording.</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n">
+          <t>(Disclosure: I'm on the Lynkk team, which is a meeting notes tool, so weigh my vote accordingly.)</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,17 +910,17 @@
           <t>https://www.reddit.com/r/AIWritingLounge/comments/1wv37k6/do_you_use_ai_to_write_meeting_notes_or_do_you/</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>r/AIWritingLounge</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>u/No-Tap-6768</t>
         </is>
@@ -930,7 +930,7 @@
           <t>Do you use AI to write meeting notes, or do you prefer summarizing them yourself?</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Title-only poll. Short engagement reply.</t>
         </is>
@@ -940,13 +940,13 @@
           <t>Both works best. Let AI capture everything so you can pay attention in the meeting, then spend two minutes after the call checking the action items and decisions against the recording. Writing a few lines in your own words afterwards still helps you remember what matters. The AI part is the record, the summary in my head is the understanding.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -959,22 +959,22 @@
           <t>https://www.reddit.com/r/PLAUDAI/comments/1x0n25s/plaud_ai_vs_claude_vs_gemini/</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>r/PLAUDAI</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>u/noodleJam-EU</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Plaud Ai vs Claude vs Gemini</t>
         </is>
@@ -989,13 +989,13 @@
           <t>Interesting test. One thing I'd add: the gap between tools often shrinks a lot when the prompt asks for a fixed structure (decisions, action items with owner and date, open questions, risks) instead of a general summary, so it may be worth running Plaud's custom template with the same prompt you gave Claude. Speaker names matter too; 'Speaker 9' makes even a good summary hard to use. Did you check how each one handled things that were suggested but never agreed?</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="n">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
         <v>81</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1008,27 +1008,27 @@
           <t>https://www.reddit.com/r/DoesAnybodyElse/comments/1wrvmal/dae_actually_have_an_easier_life_with_ai/</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>r/DoesAnybodyElse</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>u/Parzival_b</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>DAE actually have an easier life with AI?</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>General AI discussion. Light, friendly engagement.</t>
         </is>
@@ -1038,13 +1038,13 @@
           <t>Mixed is a fair description. The tools that tend to stick are the boring ones where checking is cheap: meeting notes you can verify against the recording, and drafts you'd have rewritten anyway. The ones people drop are where checking takes as long as doing it yourself. Fact-checking every output gets a lot easier when the tool shows you exactly where each claim came from.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1057,17 +1057,17 @@
           <t>https://www.reddit.com/r/AIWorkStack/comments/1wtsh32/how_i_use_ai_workflow_automation_to_save_time/</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>r/AIWorkStack</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>u/lebron7</t>
         </is>
@@ -1089,15 +1089,15 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>I work on Lynkk, so I'm biased, but that's how we built the Jira step: it's a manual send from the note, not automatic.</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
+          <t>(I work on Lynkk, and that's how its Jira step works: you send items by hand, nothing goes in automatically.)</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1110,17 +1110,17 @@
           <t>https://www.reddit.com/r/negotiation/comments/1x1qct6/is_there_an_ai_tool_that_can_tell_me_exactly/</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>r/negotiation</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>u/belligerent_vogue</t>
         </is>
@@ -1140,13 +1140,13 @@
           <t>For phone calls, check two things before any demo: whether the tool can record your actual phone setup (softphone or dialer) with both sides on separate channels, and whether you can jump to a moment and leave a timestamped comment for the rep. Then test it on five lost deals and see if it finds the turn you'd have found yourself. If it can't find the moment the tone shifted on calls you already know well, it won't on new ones.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="n">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
         <v>81</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1159,22 +1159,22 @@
           <t>https://www.reddit.com/r/PlaudNoteUsers/comments/1x12i9y/what_ai_note_taking_apps_are_you_using_for/</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>r/PlaudNoteUsers</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>u/QuietlyKevin07</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>What AI note taking apps are you using for meetings?</t>
         </is>
@@ -1191,15 +1191,15 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>I work on Lynkk, so I'm biased: its brief has takeaways with timestamps that play the recording from that moment, and each recording can run up to 2 hours.</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n">
+          <t>(Disclosure: I work on Lynkk. Its notes have timestamps you can click to replay, and a recording can run up to 2 hours.)</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1212,17 +1212,17 @@
           <t>https://www.reddit.com/r/LocalLLM/comments/1x2918k/hardware_and_llm_choice_for_business_ops_project/</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>r/LocalLLM</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>u/Hefty-Divide7339</t>
         </is>
@@ -1242,13 +1242,13 @@
           <t>For minutes from recordings, the model size matters less than the pipeline: a good local transcription model with speaker labels, then a fixed minutes template (attendees, decisions, actions with owner and date, open points) fed to the LLM. A mid-size model handles that well; the big models earn their keep on the contract analysis side. I'd benchmark with one real meeting rather than fake contracts, since speaker attribution is usually where it breaks.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
         <v>73</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1261,17 +1261,17 @@
           <t>https://www.reddit.com/r/LocalLLaMA/comments/1wwnpxj/anyone_using_a_local_ai_meeting_notes_setup/</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>r/LocalLLaMA</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>u/Sash17</t>
         </is>
@@ -1281,7 +1281,7 @@
           <t>Anyone using a local AI meeting notes setup instead of Fathom?</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Wants a local setup. Engage only; no product.</t>
         </is>
@@ -1291,13 +1291,13 @@
           <t>Whisper plus a local LLM works, but the parts that take effort are speaker labels and search. Record your mic and the system audio on separate channels so 'you' and 'others' are clean, run diarization only on the others channel, and store transcripts as plain files with the summary on top so search stays simple. The summary prompt matters more than the model: a fixed structure of decisions, actions and open questions beats 'summarize this'.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="n">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1310,17 +1310,17 @@
           <t>https://www.reddit.com/r/PLAUDAI/comments/1x1tha4/lawyers_using_plaud_or_other_ai_notetakers_for/</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>r/PLAUDAI</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>u/lookamazed</t>
         </is>
@@ -1340,13 +1340,13 @@
           <t>Verbosity usually improves more from limits than from longer templates: cap each section (5 decisions, 5 actions, 3 open questions), ask for owner and date on every action, and tell it to leave out anything not explicitly agreed. Asking for a quote or timestamp next to each decision also cuts the padding, because the model can't pad what it has to cite.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="n">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1359,17 +1359,17 @@
           <t>https://www.reddit.com/r/AIVoice_Agents/comments/1x1quo3/is_anyone_using_ai_voice_tools_to_help_support/</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>r/AIVoice_Agents</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>u/scandalous_mohamed</t>
         </is>
@@ -1389,13 +1389,13 @@
           <t>The call notes part is usually the easiest win: automatic summaries with the customer's issue, what was promised and next steps cut after-call work a lot. Real-time suggestions are harder; they're only useful if the knowledge base is clean, otherwise reps learn to ignore them within a week. I'd pilot notes first, then add live prompts for the two or three call types that cause most holds.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="n">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
         <v>67</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1408,22 +1408,22 @@
           <t>https://www.reddit.com/r/PMCareers/comments/1wiznmp/is_it_my_pm_skills_or_this_org_is_an_absolute_mess/</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>r/PMCareers</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>u/Sad_Impress4747</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Is it my PM skills or this org is an absolute mess?</t>
         </is>
@@ -1438,13 +1438,13 @@
           <t>Taking notes and chasing dependencies is normal early in a PMO, but owning 40 to 70 projects with no context is not. One practical tip: send the report within an hour, with three headings (decisions, actions with owner and date, open questions) and ask attendees to correct it by end of day. It turns note-taking into the record people rely on, which is how you start getting pulled in earlier.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="n">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1457,17 +1457,17 @@
           <t>https://www.reddit.com/r/ChatGPT/comments/1wm4p5t/why_does_ai_sometimes_make_my_summary_longer_than/</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>r/ChatGPT</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>u/yi111</t>
         </is>
@@ -1477,7 +1477,7 @@
           <t>Why does AI sometimes make my “summary” longer than the thing I wanted summarized?</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>ChatGPT summary length discussion. Light engagement.</t>
         </is>
@@ -1487,8 +1487,8 @@
           <t>Ruthless cut, usually. What works is giving it a shape instead of a length: 'three decisions, three actions with owners, anything unresolved, nothing else'. Completeness creeps back in when the prompt is open-ended. For meetings specifically, separating what was agreed from what was only discussed cuts the length more than any word limit.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="n">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
         <v>53</v>
       </c>
     </row>

--- a/lynkk-reddit-leads/results/2026-10-11/engagement_replies_2026-10-11.xlsx
+++ b/lynkk-reddit-leads/results/2026-10-11/engagement_replies_2026-10-11.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>(Disclosure: I'm on the Lynkk team, which is a meeting notes tool, so weigh my vote accordingly.)</t>
+          <t>Lynkk is one meeting notes tool built around that timestamp idea, if you're comparing.</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>(I work on Lynkk, and that's how its Jira step works: you send items by hand, nothing goes in automatically.)</t>
+          <t>Lynkk's Jira step works that way: items are sent by hand, nothing goes in automatically.</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>(Disclosure: I work on Lynkk. Its notes have timestamps you can click to replay, and a recording can run up to 2 hours.)</t>
+          <t>Lynkk's notes have timestamps you can click to replay, and a recording can run up to 2 hours.</t>
         </is>
       </c>
       <c r="K15" t="n">

--- a/lynkk-reddit-leads/results/2026-10-11/engagement_replies_2026-10-11.xlsx
+++ b/lynkk-reddit-leads/results/2026-10-11/engagement_replies_2026-10-11.xlsx
@@ -427,20 +427,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1490,6 +1490,104 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
         <v>53</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/AIAssisted/comments/1x36z0d/whats_the_most_useful_thing_your_ai_recorder/</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/AIAssisted/comments/1x36z0d/whats_the_most_useful_thing_your_ai_recorder/</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>r/AIAssisted</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>u/Comfortable-Pay611</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>What’s the most useful thing your AI recorder gives you after a meeting?</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Discussion about which AI recorder output people actually use.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>A follow-up that's basically ready to send wins for most people, but only if it's built from the action items rather than the summary. The summary is for whoever missed the meeting; the action items with owners and dates are what you actually send to the client. Asking for 'decisions, action items with owner and date, and open questions' as the output shape gets you most of the way to that email.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/ConstructionManagers/comments/1vm1lxg/what_tools_help_you_be_more_efficient_and/</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/ConstructionManagers/comments/1vm1lxg/what_tools_help_you_be_more_efficient_and/</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>r/ConstructionManagers</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>u/Bobcatbob9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>What tools help you be more efficient and effective as a PM.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Construction PM on four projects asking what tools help; meeting minutes is one concrete win.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Meeting minutes is the easiest one to take off your plate first. Record the OAC and sub meetings (with permission), let a tool draft minutes with action items, owners and dates, then spend five minutes correcting it before it goes out. That alone usually gives back a few hours a week. Copilot can help with drafting submittal logs and emails if you already have it. Congrats on the newborn, and protect that time off.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1534,6 +1632,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
